--- a/MRP_Model_Scores.xlsx
+++ b/MRP_Model_Scores.xlsx
@@ -408,7 +408,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>11146.64316836144</v>
+        <v>9222.002126573263</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -416,7 +416,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>105.5776641546944</v>
+        <v>96.03125598769009</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -424,7 +424,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>36.273473190049</v>
+        <v>32.47495980990135</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -432,7 +432,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.5415424393730348</v>
+        <v>0.6207022567075713</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -440,7 +440,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>6.963165454073729</v>
+        <v>6.217637074391543</v>
       </c>
     </row>
   </sheetData>
